--- a/filesystem/MarketingOps/Reporting/Q1_2026_vendor_spend_pacing.xlsx
+++ b/filesystem/MarketingOps/Reporting/Q1_2026_vendor_spend_pacing.xlsx
@@ -181,7 +181,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -273,11 +273,44 @@
         <color rgb="000F172A"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BAE6FD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BAE6FD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BAE6FD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BAE6FD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BAE6FD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BAE6FD"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -423,6 +456,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -744,7 +778,6 @@
           <t>THORNFIELD LIFE SCIENCES MARKETING</t>
         </is>
       </c>
-      <c r="B1" s="25" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="26" t="inlineStr">
@@ -752,7 +785,6 @@
           <t>Q1 2026 Vendor Spend Pacing Report — MedTech AdNetwork (IO-MTAN-2025-Q4-014 / renewal)</t>
         </is>
       </c>
-      <c r="B2" s="26" t="n"/>
     </row>
     <row r="3" ht="14" customHeight="1"/>
     <row r="4" ht="24" customHeight="1">
@@ -903,10 +935,10 @@
     <row r="17" ht="75" customHeight="1">
       <c r="A17" s="29" t="inlineStr">
         <is>
-          <t>Weekly pacing tracker for the MedTech AdNetwork programmatic display placement against the Q1 2026 vendor floor commitment carried on the IO. Committed floor is expressed on a $/wk equivalent basis derived from the $15,000/month contractual minimum prorated across the 13 weeks of Q1 2026 ($45,000 / 13 = $3,461.54/wk). January weeks reflect actual weekly delivery drawn from the vendor pacing feed; February and March weeks reflect projected commitment at the floor rate.</t>
-        </is>
-      </c>
-      <c r="B17" s="29" t="n"/>
+          <t>Weekly pacing tracker for the MedTech AdNetwork programmatic display placement against the Q1 2026 vendor floor commitment carried on the IO. Committed floor is expressed on a $/wk equivalent basis derived from the $15,000/month contractual minimum prorated across the 13 weeks of Q1 2026 ($45,000 / 13 = $3,461.54/wk). The 01/05 and 01/12 January weeks (through the anchor date) reflect actual weekly delivery drawn from the vendor pacing feed; the remaining January weeks, and all February and March weeks, reflect projected commitment at the floor rate.</t>
+        </is>
+      </c>
+      <c r="B17" s="51" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -943,12 +975,6 @@
           <t>Weekly pacing — Q1 2026</t>
         </is>
       </c>
-      <c r="B1" s="25" t="n"/>
-      <c r="C1" s="25" t="n"/>
-      <c r="D1" s="25" t="n"/>
-      <c r="E1" s="25" t="n"/>
-      <c r="F1" s="25" t="n"/>
-      <c r="G1" s="25" t="n"/>
     </row>
     <row r="2" ht="14" customHeight="1"/>
     <row r="3" ht="34" customHeight="1">
@@ -1065,7 +1091,7 @@
       </c>
       <c r="G6" s="28" t="inlineStr">
         <is>
-          <t>Actual — week 3</t>
+          <t>Projected commitment — week 3</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1118,7 @@
       </c>
       <c r="G7" s="39" t="inlineStr">
         <is>
-          <t>Actual — week 4; Jan floor fully consumed</t>
+          <t>Projected commitment — week 4; Jan floor projected fully consumed</t>
         </is>
       </c>
     </row>
@@ -1397,10 +1423,6 @@
           <t>Q1 2026 Commitment Summary</t>
         </is>
       </c>
-      <c r="B1" s="25" t="n"/>
-      <c r="C1" s="25" t="n"/>
-      <c r="D1" s="25" t="n"/>
-      <c r="E1" s="25" t="n"/>
     </row>
     <row r="2" ht="14" customHeight="1"/>
     <row r="3" ht="34" customHeight="1">
@@ -1498,7 +1520,6 @@
           <t>Notes</t>
         </is>
       </c>
-      <c r="B1" s="25" t="n"/>
     </row>
     <row r="2" ht="14" customHeight="1"/>
     <row r="3" ht="52" customHeight="1">

--- a/filesystem/MarketingOps/Reporting/Q1_2026_vendor_spend_pacing.xlsx
+++ b/filesystem/MarketingOps/Reporting/Q1_2026_vendor_spend_pacing.xlsx
@@ -874,7 +874,7 @@
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="27" t="inlineStr">
         <is>
-          <t>Anchor period</t>
+          <t>Reporting period</t>
         </is>
       </c>
       <c r="B11" s="28" t="inlineStr">
@@ -935,7 +935,7 @@
     <row r="17" ht="75" customHeight="1">
       <c r="A17" s="29" t="inlineStr">
         <is>
-          <t>Weekly pacing tracker for the MedTech AdNetwork programmatic display placement against the Q1 2026 vendor floor commitment carried on the IO. Committed floor is expressed on a $/wk equivalent basis derived from the $15,000/month contractual minimum prorated across the 13 weeks of Q1 2026 ($45,000 / 13 = $3,461.54/wk). The 01/05 and 01/12 January weeks (through the anchor date) reflect actual weekly delivery drawn from the vendor pacing feed; the remaining January weeks, and all February and March weeks, reflect projected commitment at the floor rate.</t>
+          <t>Weekly pacing tracker for the MedTech AdNetwork programmatic display placement against the Q1 2026 vendor floor commitment carried on the IO. Committed floor is expressed on a $/wk equivalent basis derived from the $15,000/month contractual minimum prorated across the 13 weeks of Q1 2026 ($45,000 / 13 = $3,461.54/wk). The 01/05 and 01/12 January weeks (through the 01/12/2026 report date) reflect actual weekly delivery drawn from the vendor pacing feed; the remaining January weeks, and all February and March weeks, reflect projected commitment at the floor rate.</t>
         </is>
       </c>
       <c r="B17" s="51" t="n"/>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="G5" s="39" t="inlineStr">
         <is>
-          <t>Actual — week 2 (anchor week)</t>
+          <t>Actual — week 2 (report date)</t>
         </is>
       </c>
     </row>

--- a/filesystem/MarketingOps/Reporting/Q1_2026_vendor_spend_pacing.xlsx
+++ b/filesystem/MarketingOps/Reporting/Q1_2026_vendor_spend_pacing.xlsx
@@ -1345,19 +1345,19 @@
         </is>
       </c>
       <c r="B16" s="34" t="n">
-        <v>3461.54</v>
+        <v>3461.52</v>
       </c>
       <c r="C16" s="34" t="n">
-        <v>3461.54</v>
+        <v>3461.52</v>
       </c>
       <c r="D16" s="35" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="34" t="n">
-        <v>45000.02</v>
+        <v>45000</v>
       </c>
       <c r="F16" s="34" t="n">
-        <v>45000.02</v>
+        <v>45000</v>
       </c>
       <c r="G16" s="28" t="inlineStr">
         <is>
@@ -1372,19 +1372,19 @@
         </is>
       </c>
       <c r="B17" s="41" t="n">
-        <v>45000.02</v>
+        <v>45000</v>
       </c>
       <c r="C17" s="41" t="n">
-        <v>45000.02</v>
+        <v>45000</v>
       </c>
       <c r="D17" s="41" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="41" t="n">
-        <v>45000.02</v>
+        <v>45000</v>
       </c>
       <c r="F17" s="41" t="n">
-        <v>45000.02</v>
+        <v>45000</v>
       </c>
       <c r="G17" s="42" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
       <c r="B7" s="46" t="n"/>
       <c r="C7" s="46" t="n"/>
       <c r="D7" s="47" t="n">
-        <v>45000.02</v>
+        <v>45000</v>
       </c>
       <c r="E7" s="42" t="inlineStr">
         <is>

--- a/filesystem/MarketingOps/Reporting/Q1_2026_vendor_spend_pacing.xlsx
+++ b/filesystem/MarketingOps/Reporting/Q1_2026_vendor_spend_pacing.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00;[Red]-&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -113,6 +113,18 @@
       <name val="Segoe UI"/>
       <i val="1"/>
       <color rgb="0064748B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FF1E40AF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="FF475569"/>
       <sz val="9.5"/>
     </font>
   </fonts>
@@ -310,7 +322,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -457,6 +469,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -819,7 +837,7 @@
       </c>
       <c r="B6" s="28" t="inlineStr">
         <is>
-          <t>Life Sciences OEM — Programmatic Display (CMP-2026-0012)</t>
+          <t>Larchfield Bioanalytics — Programmatic Display (CMP-2026-0012)</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1541,7 @@
     </row>
     <row r="2" ht="14" customHeight="1"/>
     <row r="3" ht="52" customHeight="1">
-      <c r="A3" s="48" t="inlineStr">
+      <c r="A3" s="52" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
@@ -1535,7 +1553,7 @@
       </c>
     </row>
     <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="48" t="inlineStr">
+      <c r="A4" s="52" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
@@ -1547,7 +1565,7 @@
       </c>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="48" t="inlineStr">
+      <c r="A5" s="52" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
@@ -1560,7 +1578,7 @@
     </row>
     <row r="6" ht="14" customHeight="1"/>
     <row r="7" ht="20" customHeight="1">
-      <c r="B7" s="50" t="inlineStr">
+      <c r="B7" s="53" t="inlineStr">
         <is>
           <t>End of report.</t>
         </is>
